--- a/research/contacts_russia.xlsx
+++ b/research/contacts_russia.xlsx
@@ -6065,7 +6065,7 @@
       <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>Телефоны (опубликованы как контакты): +7 (952) 820-16-09, +7 (928) 039-37-18. Адрес: Краснодар, ул. Карасунская, 93. VK-сообщество у этой мастерской есть (страница-визитка построена на нём), но точный URL в источнике не раскрыт — не указываю, чтобы не выдумывать ссылку.</t>
+          <t>Телефоны (опубликованы как контакты): +7 (952) 820-16-09, +7 (928) 039-37-18. Адрес: Краснодар, ул. Карасунская, 93.</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
